--- a/output/看屋檢查清單_新北建案_2026-10-09_三_產品與坪數.xlsx
+++ b/output/看屋檢查清單_新北建案_2026-10-09_三_產品與坪數.xlsx
@@ -231,7 +231,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>資料搜尋日期：2026-10-09　|　來源：591／樂居／樂屋網／5168／住展／Mobile01／建商官網／政府圖資　|　【試算】貸8成30年2.321%（央行統計2026/8五大銀行新承做平均，7月為2.29%）；新青安3.0自2026/8/1上路，一段式機動利率1.775%起、上限1000萬，第4年起補貼遞減、第6年期滿｜稅費≒總價1~1.5%｜保固：結構15年、設備1年（自交屋起）｜履約保證法定五擇一｜斷層：北盆地僅山腳斷層(第二類)　|　【現場確認】＝公開資料查無，須向代銷索取或調謄本　|　查詢：土壤液化 liquid.net.tw／soil.taipei；淹水 dmap.ncdr.nat.gov.tw；新北液化圖資第1期板橋三重等、第2期中和土城新店等　|　治安為網路整理之113年新北各區犯罪率分級，非警政署原表　|　!＝風險提醒　+＝正面條件（原⚠️／✅）</t>
+          <t>資料搜尋日期：2026-10-09　|　來源：591／樂居／樂屋網／5168／住展／Mobile01／建商官網／政府圖資　|　【試算】貸8成30年2.321%（央行統計2026/8五大銀行新承做平均，7月為2.29%）；新青安3.0自2026/8/1上路，一段式機動利率1.775%起、上限1000萬，第4年起補貼遞減、第6年期滿｜稅費≒總價1~1.5%｜保固：結構15年、設備1年（自交屋起）｜履約保證法定五擇一｜斷層：北盆地僅山腳斷層(第二類)　|　【現場確認】＝公開資料查無，須向代銷索取或調謄本　|　查詢：土壤液化 liquid.net.tw／soil.taipei；淹水 dmap.ncdr.nat.gov.tw；新北液化圖資第1期板橋三重等、第2期中和土城新店等　|　治安為網路整理之113年新北各區犯罪率分級，非警政署原表　|　!＝風險提醒　+＝正面條件（原⚠️／✅）；實登：ToEstate(至2026-07)</t>
         </is>
       </c>
     </row>
